--- a/templates/contracts/Akt_water.xlsx
+++ b/templates/contracts/Akt_water.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\templates\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A5B396-1930-40C5-A655-8735DB14B8E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF02A5CC-01C4-47DE-B7DA-E06864C5E38D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="13650" windowHeight="20715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Членов комиссии:</t>
   </si>
   <si>
-    <t xml:space="preserve">Представителей от: </t>
-  </si>
-  <si>
     <t>Подписи:</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>Вода питьевая «Источник Старо  мытищенский премиум»</t>
+  </si>
+  <si>
+    <t>Представителей от: {{SCHOOL_LIST}}</t>
   </si>
 </sst>
 </file>
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -236,26 +236,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,12 +546,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:L29"/>
+  <dimension ref="A3:L30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="10.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="8.5703125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -550,7 +562,7 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="3"/>
@@ -562,13 +574,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E5" s="11" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E5" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -581,145 +593,173 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="135.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="2:9" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="145.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="2:9" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
+    <row r="28" spans="2:9" ht="93.75" x14ac:dyDescent="0.3">
+      <c r="C28" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="5" t="s">
+      <c r="D28" s="4"/>
+      <c r="G28" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="G27" s="6" t="s">
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="5"/>
+      <c r="D29" s="4"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="5"/>
-      <c r="D28" s="4"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
+  <mergeCells count="11">
+    <mergeCell ref="B13:I15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B17:I17"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
